--- a/data/trans_orig/P0801-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2007</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602306</t>
+          <t>603542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>634671</t>
+          <t>635900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>525349</t>
+          <t>522766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>564974</t>
+          <t>564083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1136489</t>
+          <t>1139490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1190149</t>
+          <t>1191364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69927</t>
+          <t>69398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93502</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131906</t>
+          <t>132557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142947</t>
+          <t>142788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192111</t>
+          <t>187928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30887</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68925</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832432</t>
+          <t>832259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>872943</t>
+          <t>872885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>736692</t>
+          <t>734025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>787021</t>
+          <t>787446</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1580804</t>
+          <t>1582741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1645701</t>
+          <t>1647883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60374</t>
+          <t>60282</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94445</t>
+          <t>95584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140591</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>188024</t>
+          <t>187422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>210998</t>
+          <t>210342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>269742</t>
+          <t>267242</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>22709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45465</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56714</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>94508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>577451</t>
+          <t>574813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>611056</t>
+          <t>611080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>493505</t>
+          <t>493034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>536820</t>
+          <t>537691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1082440</t>
+          <t>1084778</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1139582</t>
+          <t>1139011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46683</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103277</t>
+          <t>102783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141393</t>
+          <t>142493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156228</t>
+          <t>160063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206795</t>
+          <t>208658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>34435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54024</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>822644</t>
+          <t>821101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>859155</t>
+          <t>857590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>802184</t>
+          <t>803714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>854281</t>
+          <t>857574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1640335</t>
+          <t>1639358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1704059</t>
+          <t>1700430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59154</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91761</t>
+          <t>91022</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123766</t>
+          <t>122243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167515</t>
+          <t>168033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191331</t>
+          <t>192803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245168</t>
+          <t>245632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37971</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>47961</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>79631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>74228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108817</t>
+          <t>110599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2876172</t>
+          <t>2876209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2943079</t>
+          <t>2946110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2603467</t>
+          <t>2605295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2703467</t>
+          <t>2701280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5500015</t>
+          <t>5510525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5624881</t>
+          <t>5624915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235373</t>
+          <t>233979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>294603</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>499517</t>
+          <t>501078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>582911</t>
+          <t>587800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>751247</t>
+          <t>751730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>859559</t>
+          <t>855295</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>84180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120021</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250157</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316877</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2012</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>577186</t>
+          <t>574907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>613925</t>
+          <t>614312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>480033</t>
+          <t>481082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>527455</t>
+          <t>528804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1070162</t>
+          <t>1068622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1133644</t>
+          <t>1130564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86638</t>
+          <t>88344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106546</t>
+          <t>105119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150094</t>
+          <t>145623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169447</t>
+          <t>170994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222927</t>
+          <t>224571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50022</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82379</t>
+          <t>82289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83962</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>124857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>827764</t>
+          <t>829611</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>878234</t>
+          <t>878805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752159</t>
+          <t>750631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>806821</t>
+          <t>802799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1593344</t>
+          <t>1595688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1670435</t>
+          <t>1669097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87408</t>
+          <t>86690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128165</t>
+          <t>126392</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132169</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178792</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231700</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>291092</t>
+          <t>296371</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72802</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80200</t>
+          <t>79914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119566</t>
+          <t>119070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130291</t>
+          <t>130844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180451</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644805</t>
+          <t>643190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>683443</t>
+          <t>684089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>569236</t>
+          <t>566714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>616848</t>
+          <t>619222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1227726</t>
+          <t>1230470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291232</t>
+          <t>1292709</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75458</t>
+          <t>75348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90969</t>
+          <t>91631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132095</t>
+          <t>133286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144082</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193734</t>
+          <t>193953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48991</t>
+          <t>47242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56738</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>91733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84941</t>
+          <t>86556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130403</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>784802</t>
+          <t>783321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>830425</t>
+          <t>831158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>747538</t>
+          <t>748636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>804778</t>
+          <t>806053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1547909</t>
+          <t>1550874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1622237</t>
+          <t>1622812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>81082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>122252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165288</t>
+          <t>166640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217110</t>
+          <t>214745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258628</t>
+          <t>259870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>324264</t>
+          <t>320780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54272</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>68933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103495</t>
+          <t>103644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103933</t>
+          <t>102375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>146114</t>
+          <t>147275</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2881909</t>
+          <t>2881731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2967223</t>
+          <t>2967405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2603398</t>
+          <t>2608515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2709062</t>
+          <t>2712998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5504372</t>
+          <t>5513816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5646540</t>
+          <t>5647275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>301580</t>
+          <t>299585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>369805</t>
+          <t>371052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>535995</t>
+          <t>534866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>626076</t>
+          <t>625028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>857992</t>
+          <t>855193</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977917</t>
+          <t>975111</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139269</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>192022</t>
+          <t>194331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287872</t>
+          <t>286207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>355099</t>
+          <t>356685</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>442895</t>
+          <t>443843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>533913</t>
+          <t>531141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2016</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>548938</t>
+          <t>551866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>587526</t>
+          <t>588612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>468710</t>
+          <t>469286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>515889</t>
+          <t>516302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1032620</t>
+          <t>1032479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1091732</t>
+          <t>1091128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>55879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89137</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95760</t>
+          <t>94080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133317</t>
+          <t>136423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159371</t>
+          <t>161057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212900</t>
+          <t>211852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52772</t>
+          <t>53701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86062</t>
+          <t>85782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82396</t>
+          <t>83314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120678</t>
+          <t>120897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>847264</t>
+          <t>849321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>893912</t>
+          <t>893184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768715</t>
+          <t>767418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>826663</t>
+          <t>825134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1634064</t>
+          <t>1631759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1711736</t>
+          <t>1707099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129539</t>
+          <t>130517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133388</t>
+          <t>130959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182924</t>
+          <t>179408</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231284</t>
+          <t>233502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>295297</t>
+          <t>296935</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>55930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110522</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110398</t>
+          <t>110514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158834</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>640910</t>
+          <t>641968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>679487</t>
+          <t>678526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>595621</t>
+          <t>597334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>644703</t>
+          <t>644696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1250427</t>
+          <t>1252394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1312525</t>
+          <t>1314088</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52586</t>
+          <t>54855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>87204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83132</t>
+          <t>81076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122469</t>
+          <t>121526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196514</t>
+          <t>195540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79401</t>
+          <t>79446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73083</t>
+          <t>73757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111506</t>
+          <t>112634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>799306</t>
+          <t>801360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>839468</t>
+          <t>841337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>801569</t>
+          <t>801341</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>853881</t>
+          <t>859494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1612958</t>
+          <t>1614094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1682909</t>
+          <t>1685069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>59623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92888</t>
+          <t>92274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>111593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157573</t>
+          <t>155615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182531</t>
+          <t>184074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237623</t>
+          <t>239216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56766</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62567</t>
+          <t>63586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100640</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98875</t>
+          <t>100404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144607</t>
+          <t>144977</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2881758</t>
+          <t>2877214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2960466</t>
+          <t>2961766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2689490</t>
+          <t>2690030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2795589</t>
+          <t>2792964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5595361</t>
+          <t>5599692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5727800</t>
+          <t>5733595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>292558</t>
+          <t>289822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>362239</t>
+          <t>361242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>457093</t>
+          <t>458988</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>543704</t>
+          <t>543207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>772737</t>
+          <t>768341</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>876990</t>
+          <t>881772</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124595</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171432</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265319</t>
+          <t>266832</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336190</t>
+          <t>336917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>404263</t>
+          <t>404517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>493691</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2023</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>512629</t>
+          <t>511092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>548593</t>
+          <t>548602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>551975</t>
+          <t>552949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>604578</t>
+          <t>604248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1075294</t>
+          <t>1075643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1138354</t>
+          <t>1133214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51401</t>
+          <t>50462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>79866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>72102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106957</t>
+          <t>104827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130780</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175205</t>
+          <t>177183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54384</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73719</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>86126</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122924</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460340</t>
+          <t>410313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1067368</t>
+          <t>1066433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730791</t>
+          <t>730469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>768419</t>
+          <t>769531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1082414</t>
+          <t>1068357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1801227</t>
+          <t>1804863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86041</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>712828</t>
+          <t>768349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>121743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155761</t>
+          <t>155428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233513</t>
+          <t>230460</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>995142</t>
+          <t>1003571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58541</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82808</t>
+          <t>83023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68488</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122959</t>
+          <t>122289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>556717</t>
+          <t>559252</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>599931</t>
+          <t>600843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>731390</t>
+          <t>733038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>854193</t>
+          <t>858908</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1315086</t>
+          <t>1315206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1448248</t>
+          <t>1449295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80537</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118455</t>
+          <t>116647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>138638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>130600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235184</t>
+          <t>237814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>49417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93277</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769750</t>
+          <t>767876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>810122</t>
+          <t>809489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>820167</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>897913</t>
+          <t>895265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1604010</t>
+          <t>1608043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1688698</t>
+          <t>1683170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>79024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115354</t>
+          <t>115441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124466</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179913</t>
+          <t>181975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219248</t>
+          <t>222437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284505</t>
+          <t>284604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51867</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68698</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108992</t>
+          <t>107611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147526</t>
+          <t>145791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2137231</t>
+          <t>2152743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2964823</t>
+          <t>2967652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2887911</t>
+          <t>2883793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3092455</t>
+          <t>3098624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4965288</t>
+          <t>5036625</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5942834</t>
+          <t>5942376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>342667</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1223273</t>
+          <t>1199362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>400445</t>
+          <t>392132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>535604</t>
+          <t>538496</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>816643</t>
+          <t>821386</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1839966</t>
+          <t>1734167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110518</t>
+          <t>107734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>216236</t>
+          <t>220567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295695</t>
+          <t>298997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357799</t>
+          <t>353317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>452106</t>
+          <t>451446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0801-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>603542</t>
+          <t>603590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>635900</t>
+          <t>635418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>522766</t>
+          <t>522341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>564083</t>
+          <t>564924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1139490</t>
+          <t>1138446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1191364</t>
+          <t>1190315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69398</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>93801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132557</t>
+          <t>131930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142788</t>
+          <t>145297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187928</t>
+          <t>193666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21732</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43623</t>
+          <t>42991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68326</t>
+          <t>65262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832259</t>
+          <t>833513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>872885</t>
+          <t>874259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>734025</t>
+          <t>736554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>787446</t>
+          <t>788080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1582741</t>
+          <t>1579534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1647883</t>
+          <t>1645683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60282</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95584</t>
+          <t>93325</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140278</t>
+          <t>139084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>187422</t>
+          <t>187122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>210342</t>
+          <t>211549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>267242</t>
+          <t>270916</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56344</t>
+          <t>57424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59134</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94508</t>
+          <t>92677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>574813</t>
+          <t>578745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>611080</t>
+          <t>612379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>493034</t>
+          <t>494704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>537691</t>
+          <t>539324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1084778</t>
+          <t>1083147</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1139011</t>
+          <t>1142210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48071</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79945</t>
+          <t>77005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102783</t>
+          <t>99688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142493</t>
+          <t>140204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160063</t>
+          <t>152708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208658</t>
+          <t>205438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>32334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59735</t>
+          <t>60535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53536</t>
+          <t>54442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84603</t>
+          <t>84454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>821101</t>
+          <t>822747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>857590</t>
+          <t>858949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>803714</t>
+          <t>803343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>857574</t>
+          <t>854091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1639358</t>
+          <t>1637483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1700430</t>
+          <t>1699966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>58473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91022</t>
+          <t>89553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>124346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168033</t>
+          <t>172872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192803</t>
+          <t>193939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245632</t>
+          <t>248819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>49764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79631</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74228</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>110599</t>
+          <t>109579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2876209</t>
+          <t>2873378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2946110</t>
+          <t>2944631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2605295</t>
+          <t>2600192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2701280</t>
+          <t>2696356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5510525</t>
+          <t>5501381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5624915</t>
+          <t>5625201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>234104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>294603</t>
+          <t>296807</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>501078</t>
+          <t>504133</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>587800</t>
+          <t>590426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>751730</t>
+          <t>754279</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>855295</t>
+          <t>859064</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84180</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>124309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>157790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209051</t>
+          <t>210321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252141</t>
+          <t>251566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>317893</t>
+          <t>317654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>574907</t>
+          <t>575158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>614312</t>
+          <t>614791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>481082</t>
+          <t>480464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>528804</t>
+          <t>529539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1068622</t>
+          <t>1070249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1130564</t>
+          <t>1132157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>54022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88344</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105119</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145623</t>
+          <t>147191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170994</t>
+          <t>169575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224571</t>
+          <t>223903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>84649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124857</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>829611</t>
+          <t>830597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>878805</t>
+          <t>880032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>750631</t>
+          <t>748443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>802799</t>
+          <t>808324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1595688</t>
+          <t>1597052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1669097</t>
+          <t>1671543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>87235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126392</t>
+          <t>128785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>133059</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179801</t>
+          <t>181192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231365</t>
+          <t>231137</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296371</t>
+          <t>292177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71689</t>
+          <t>72680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79914</t>
+          <t>79391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119070</t>
+          <t>119405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130844</t>
+          <t>130714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178874</t>
+          <t>179513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>643190</t>
+          <t>643511</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>684089</t>
+          <t>682616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>566714</t>
+          <t>569472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>619222</t>
+          <t>616997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1230470</t>
+          <t>1227054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1292709</t>
+          <t>1292156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>45728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75348</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91631</t>
+          <t>91052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133286</t>
+          <t>131127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142672</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193953</t>
+          <t>193362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47242</t>
+          <t>48024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56476</t>
+          <t>57735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86556</t>
+          <t>86780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129891</t>
+          <t>130510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>783321</t>
+          <t>779224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>831158</t>
+          <t>828364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>748636</t>
+          <t>747569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>806053</t>
+          <t>809012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1550874</t>
+          <t>1547741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1622812</t>
+          <t>1624256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>82094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122252</t>
+          <t>122719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166640</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214745</t>
+          <t>216570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259870</t>
+          <t>254751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320780</t>
+          <t>321298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68933</t>
+          <t>66231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103644</t>
+          <t>105238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147275</t>
+          <t>147154</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2881731</t>
+          <t>2882611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2967405</t>
+          <t>2970587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2608515</t>
+          <t>2601302</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2712998</t>
+          <t>2706798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5513816</t>
+          <t>5505234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5647275</t>
+          <t>5641435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>299585</t>
+          <t>297225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>371052</t>
+          <t>370202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>534866</t>
+          <t>536321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>625028</t>
+          <t>623519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>855193</t>
+          <t>859213</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975111</t>
+          <t>969028</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141356</t>
+          <t>141259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194331</t>
+          <t>196134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286207</t>
+          <t>286307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356685</t>
+          <t>359176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443843</t>
+          <t>443201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>531141</t>
+          <t>538790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>551866</t>
+          <t>550048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>588612</t>
+          <t>588605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>469286</t>
+          <t>469921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>516302</t>
+          <t>516964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1032479</t>
+          <t>1028365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1091128</t>
+          <t>1090728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>55872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>90083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94080</t>
+          <t>92703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136423</t>
+          <t>133504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161057</t>
+          <t>160740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211852</t>
+          <t>212416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>52032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85782</t>
+          <t>83441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>82112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120897</t>
+          <t>119777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>849321</t>
+          <t>843756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>893184</t>
+          <t>893323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>767418</t>
+          <t>772476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>825134</t>
+          <t>828037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1631759</t>
+          <t>1630455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1707099</t>
+          <t>1704077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130517</t>
+          <t>131227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130959</t>
+          <t>130897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179408</t>
+          <t>180548</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233502</t>
+          <t>232548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296935</t>
+          <t>295458</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>31072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55930</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71752</t>
+          <t>71949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111013</t>
+          <t>112877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>111097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154402</t>
+          <t>155644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641968</t>
+          <t>642002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>678526</t>
+          <t>679121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597334</t>
+          <t>595651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>644696</t>
+          <t>643440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1252394</t>
+          <t>1253687</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1314088</t>
+          <t>1314990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54855</t>
+          <t>54316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87204</t>
+          <t>86261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81076</t>
+          <t>81654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121526</t>
+          <t>120797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144683</t>
+          <t>146470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195540</t>
+          <t>196871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40657</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79446</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112634</t>
+          <t>112095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>801360</t>
+          <t>798591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>841337</t>
+          <t>839707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>801341</t>
+          <t>802134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>859494</t>
+          <t>857691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1614094</t>
+          <t>1613075</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1685069</t>
+          <t>1685748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>59545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>93695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111593</t>
+          <t>111205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155615</t>
+          <t>157386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184074</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239216</t>
+          <t>239139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63586</t>
+          <t>63869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>99808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100404</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144977</t>
+          <t>146733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2877214</t>
+          <t>2882276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2961766</t>
+          <t>2961057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2690030</t>
+          <t>2686179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2792964</t>
+          <t>2794762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5599692</t>
+          <t>5596147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5733595</t>
+          <t>5738098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>289822</t>
+          <t>291365</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>362002</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>458988</t>
+          <t>461591</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>543207</t>
+          <t>547083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>768341</t>
+          <t>768934</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>881772</t>
+          <t>879884</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123579</t>
+          <t>124676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171287</t>
+          <t>170693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266832</t>
+          <t>263048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336917</t>
+          <t>337618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>404517</t>
+          <t>401607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>486863</t>
+          <t>493682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>531146</t>
+          <t>576009</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>511092</t>
+          <t>554937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>548602</t>
+          <t>594109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>571753</t>
+          <t>568951</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>552949</t>
+          <t>550424</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>604248</t>
+          <t>584955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1102899</t>
+          <t>1144959</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1075643</t>
+          <t>1117654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1133214</t>
+          <t>1168144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63431</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>55674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79866</t>
+          <t>86550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91368</t>
+          <t>97802</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104827</t>
+          <t>112069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>154800</t>
+          <t>167555</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133283</t>
+          <t>146750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177183</t>
+          <t>188114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40864</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62209</t>
+          <t>67427</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>56630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>79810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>103073</t>
+          <t>112375</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86126</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>131411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>841338</t>
+          <t>931231</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410313</t>
+          <t>906707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1066433</t>
+          <t>950550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749476</t>
+          <t>840155</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730469</t>
+          <t>818264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>769531</t>
+          <t>862795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1590815</t>
+          <t>1771386</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1068357</t>
+          <t>1740700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1804863</t>
+          <t>1800930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>318553</t>
+          <t>80647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>768349</t>
+          <t>100366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138591</t>
+          <t>153574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121743</t>
+          <t>134879</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155428</t>
+          <t>172870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>457144</t>
+          <t>234221</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>230460</t>
+          <t>209029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1003571</t>
+          <t>261656</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>49369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70039</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58844</t>
+          <t>64851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83023</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>103012</t>
+          <t>114148</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68138</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122289</t>
+          <t>131326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>579804</t>
+          <t>666270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>559252</t>
+          <t>643120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>600843</t>
+          <t>687974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>784864</t>
+          <t>640854</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>733038</t>
+          <t>620164</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>858908</t>
+          <t>658743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1364669</t>
+          <t>1307124</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1315206</t>
+          <t>1275908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1449295</t>
+          <t>1335501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97272</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79629</t>
+          <t>86238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116647</t>
+          <t>126032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>115720</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>100718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138638</t>
+          <t>133860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>220968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130600</t>
+          <t>195448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237814</t>
+          <t>249895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>46138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65522</t>
+          <t>68279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49417</t>
+          <t>72057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>105754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>790720</t>
+          <t>848763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>767876</t>
+          <t>827138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>809489</t>
+          <t>868497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>849777</t>
+          <t>854108</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>821351</t>
+          <t>830729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>895265</t>
+          <t>878410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1640497</t>
+          <t>1702872</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1608043</t>
+          <t>1674592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1683170</t>
+          <t>1736552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96239</t>
+          <t>99679</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79024</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115441</t>
+          <t>119163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>157536</t>
+          <t>165652</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126368</t>
+          <t>147036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181975</t>
+          <t>184968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>253775</t>
+          <t>265331</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222437</t>
+          <t>237081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284604</t>
+          <t>291561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39872</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>31357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52679</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87620</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>84722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>115848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>127492</t>
+          <t>140901</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>123741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145791</t>
+          <t>159817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2743009</t>
+          <t>3022273</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2152743</t>
+          <t>2978377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2967652</t>
+          <t>3062900</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2955870</t>
+          <t>2904068</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2883793</t>
+          <t>2862764</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3098624</t>
+          <t>2943458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5698879</t>
+          <t>5926342</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5036625</t>
+          <t>5868583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5942376</t>
+          <t>5986143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>575495</t>
+          <t>355326</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>342667</t>
+          <t>323363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1199362</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>489021</t>
+          <t>532748</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>392132</t>
+          <t>501044</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>538496</t>
+          <t>565516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1064516</t>
+          <t>888074</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>821386</t>
+          <t>839471</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1734167</t>
+          <t>940931</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155163</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>134102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165951</t>
+          <t>180147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>266844</t>
+          <t>299501</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220567</t>
+          <t>275315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298997</t>
+          <t>324529</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>408157</t>
+          <t>454664</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>353317</t>
+          <t>422844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>451446</t>
+          <t>493072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
